--- a/backtest_runs/20260410_193731/by_symbol/KAPCO/KAPCO.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/KAPCO/KAPCO.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1486.399999999995</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98513.60000000001</v>
@@ -679,7 +679,7 @@
         <v>-5425.360000000003</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>98142</v>
@@ -771,7 +771,7 @@
         <v>-111.4800000000042</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>102972.8</v>
@@ -817,7 +817,7 @@
         <v>-408.7599999999979</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>102564.04</v>
@@ -863,7 +863,7 @@
         <v>-6465.840000000007</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>96098.2</v>
@@ -909,7 +909,7 @@
         <v>-2118.120000000001</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>93980.08</v>
@@ -1047,7 +1047,7 @@
         <v>-483.0799999999963</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>94351.68000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-2378.240000000002</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>93571.32000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-74.31999999999842</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>93497</v>
@@ -1277,7 +1277,7 @@
         <v>-5908.44</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>87588.56</v>
@@ -1415,7 +1415,7 @@
         <v>-817.520000000009</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>92047.75999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-111.479999999991</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>91936.28000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-297.2800000000069</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>91639</v>
@@ -1645,7 +1645,7 @@
         <v>-3344.400000000008</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>97435.95999999999</v>
